--- a/koyama/practice03/practice03エビデンス.xlsx
+++ b/koyama/practice03/practice03エビデンス.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29816"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="38" documentId="11_31802F1733C7A0836B02CE998F682C9D7A7B838F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34B828D1-875B-4813-95FF-96340B1CDAB9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D409A47-2996-4C0F-BAD7-017C534AA3EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -120,17 +120,20 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>619125</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
+        <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9012C59-F597-4ED6-BD76-44B4DE76455B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04859804-FDFF-4C9F-4075-6CA3AC9D230A}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{6D4584E9-BF21-438A-9A07-73303D8B8CA6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -147,7 +150,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4114800" y="342900"/>
-          <a:ext cx="8162925" cy="4552950"/>
+          <a:ext cx="8486775" cy="4438650"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -160,14 +163,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>666750</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -177,7 +180,7 @@
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31A3A8B4-B90D-C1D4-50ED-348B5CED1743}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{E9012C59-F597-4ED6-BD76-44B4DE76455B}"/>
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{04859804-FDFF-4C9F-4075-6CA3AC9D230A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -185,8 +188,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4095750" y="590550"/>
-          <a:ext cx="219075" cy="781050"/>
+          <a:off x="4095750" y="866775"/>
+          <a:ext cx="1047750" cy="200025"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -230,7 +233,7 @@
       <xdr:col>4</xdr:col>
       <xdr:colOff>666750</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:rowOff>109538</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
@@ -263,8 +266,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="3409950" y="981075"/>
-          <a:ext cx="685800" cy="466725"/>
+          <a:off x="3409950" y="966788"/>
+          <a:ext cx="685800" cy="481012"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
